--- a/KiCAD_files/weather_station_v5/weather_station_v5_BOM_master.xlsx
+++ b/KiCAD_files/weather_station_v5/weather_station_v5_BOM_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shiel\Documents\Github\low-power-weather-station\KiCAD_files\weather_station_lowpower\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shiel\Documents\Github\low-power-weather-station\KiCAD_files\weather_station_v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77FC794-0B8A-4240-88E2-BF9861FDBE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB2657D-8016-4C10-9D7C-7127062BE816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="0" windowWidth="20148" windowHeight="13758" xr2:uid="{37D7DDED-5265-4298-AC74-1A1E6D20F91E}"/>
+    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="13758" xr2:uid="{37D7DDED-5265-4298-AC74-1A1E6D20F91E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -668,18 +668,12 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -691,6 +685,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -700,14 +699,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1057,191 +1054,191 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="6" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="6" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="6" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="6" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="6" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="6" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="6" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="6" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="6" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="6" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="6" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="7" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1255,17 +1252,17 @@
       <c r="C16">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="8">
         <v>0.12</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="8">
         <f>C16*D16</f>
         <v>0.24</v>
       </c>
       <c r="F16" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="4" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1279,17 +1276,17 @@
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="8">
         <f t="shared" ref="E17:E52" si="0">C17*D17</f>
         <v>0.14000000000000001</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="4" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1303,17 +1300,17 @@
       <c r="C18">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="8">
         <v>0.1</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F18" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1327,17 +1324,17 @@
       <c r="C19">
         <v>1</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="8">
         <v>0.13</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="8">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
       <c r="F19" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1351,17 +1348,17 @@
       <c r="C20">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="8">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="8">
         <f t="shared" si="0"/>
         <v>1.1399999999999999</v>
       </c>
       <c r="F20" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="4" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1375,10 +1372,10 @@
       <c r="C21">
         <v>12</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F21" t="s">
@@ -1398,17 +1395,17 @@
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="8">
         <v>1.63</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="8">
         <f t="shared" si="0"/>
         <v>1.63</v>
       </c>
       <c r="F22" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1422,17 +1419,17 @@
       <c r="C23">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="8">
         <v>0.38</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="8">
         <f t="shared" si="0"/>
         <v>0.38</v>
       </c>
       <c r="F23" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1446,17 +1443,17 @@
       <c r="C24">
         <v>1</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="8">
         <v>7.5</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="8">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="F24" t="s">
         <v>84</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1470,17 +1467,17 @@
       <c r="C25">
         <v>1</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="8">
         <v>0.71</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="8">
         <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
       <c r="F25" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1494,17 +1491,17 @@
       <c r="C26">
         <v>1</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="8">
         <v>0.1</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F26" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="6" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1518,10 +1515,10 @@
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="8">
         <v>0.31</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="8">
         <f t="shared" si="0"/>
         <v>0.31</v>
       </c>
@@ -1542,17 +1539,17 @@
       <c r="C28">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="8">
         <v>0.1</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F28" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1566,17 +1563,17 @@
       <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="8">
         <v>0.1</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F29" t="s">
         <v>90</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1590,17 +1587,17 @@
       <c r="C30">
         <v>4</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="8">
         <v>0.1</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="8">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="F30" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1614,17 +1611,17 @@
       <c r="C31">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="8">
         <v>0.1</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F31" t="s">
         <v>92</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1638,17 +1635,17 @@
       <c r="C32">
         <v>1</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="8">
         <v>0.1</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F32" t="s">
         <v>93</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1662,17 +1659,17 @@
       <c r="C33">
         <v>2</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="8">
         <v>0.21</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="8">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
       <c r="F33" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1686,17 +1683,17 @@
       <c r="C34">
         <v>1</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="8">
         <v>0.8</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="8">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="F34" t="s">
         <v>95</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="6" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1710,17 +1707,17 @@
       <c r="C35">
         <v>1</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="8">
         <v>0.24</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="8">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
       <c r="F35" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1734,17 +1731,17 @@
       <c r="C36">
         <v>1</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="8">
         <v>0.2</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="8">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="6" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1758,17 +1755,17 @@
       <c r="C37">
         <v>1</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="8">
         <v>2.63</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="8">
         <f t="shared" si="0"/>
         <v>2.63</v>
       </c>
       <c r="F37" t="s">
         <v>143</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1782,17 +1779,17 @@
       <c r="C38">
         <v>1</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="8">
         <v>0.8</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="8">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="F38" t="s">
         <v>129</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1806,17 +1803,17 @@
       <c r="C39">
         <v>1</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="8">
         <v>2.27</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="8">
         <f t="shared" si="0"/>
         <v>2.27</v>
       </c>
       <c r="F39" t="s">
         <v>130</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="6" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1830,17 +1827,17 @@
       <c r="C40">
         <v>1</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="8">
         <v>13.95</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="8">
         <f t="shared" si="0"/>
         <v>13.95</v>
       </c>
       <c r="F40" t="s">
         <v>132</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1854,17 +1851,17 @@
       <c r="C41">
         <v>1</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="8">
         <v>0.42</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="8">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="6" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1878,17 +1875,17 @@
       <c r="C42">
         <v>2</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="8">
         <v>0.42</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="8">
         <f t="shared" si="0"/>
         <v>0.84</v>
       </c>
       <c r="F42" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="6" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1902,17 +1899,17 @@
       <c r="C43">
         <v>1</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="8">
         <v>14.95</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="8">
         <f t="shared" si="0"/>
         <v>14.95</v>
       </c>
       <c r="F43" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="G43" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1926,17 +1923,17 @@
       <c r="C44">
         <v>1</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="8">
         <v>5.2</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="8">
         <f t="shared" si="0"/>
         <v>5.2</v>
       </c>
       <c r="F44" t="s">
         <v>138</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1950,17 +1947,17 @@
       <c r="C45">
         <v>1</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="8">
         <v>2.89</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="8">
         <f t="shared" si="0"/>
         <v>2.89</v>
       </c>
       <c r="F45" t="s">
         <v>139</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1974,17 +1971,17 @@
       <c r="C46">
         <v>1</v>
       </c>
-      <c r="D46" s="14">
-        <v>45.91</v>
-      </c>
-      <c r="E46" s="14">
-        <f t="shared" si="0"/>
-        <v>45.91</v>
+      <c r="D46" s="8">
+        <v>68</v>
+      </c>
+      <c r="E46" s="8">
+        <f t="shared" si="0"/>
+        <v>68</v>
       </c>
       <c r="F46" t="s">
         <v>140</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1998,17 +1995,17 @@
       <c r="C47">
         <v>1</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="8">
         <v>5.4</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
         <v>5.4</v>
       </c>
       <c r="F47" t="s">
         <v>141</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2022,17 +2019,17 @@
       <c r="C48">
         <v>6</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="8">
         <v>0.05</v>
       </c>
-      <c r="E48" s="14">
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="F48" t="s">
         <v>142</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2046,17 +2043,17 @@
       <c r="C49">
         <v>1</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="8">
         <v>4.08</v>
       </c>
-      <c r="E49" s="14">
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
         <v>4.08</v>
       </c>
       <c r="F49" t="s">
         <v>46</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2070,17 +2067,17 @@
       <c r="C50">
         <v>1</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="8">
         <v>0.09</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
       <c r="F50" t="s">
         <v>146</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2094,17 +2091,17 @@
       <c r="C51">
         <v>1</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="8">
         <v>0.08</v>
       </c>
-      <c r="E51" s="14">
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
       <c r="F51" t="s">
         <v>145</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2118,17 +2115,17 @@
       <c r="C52">
         <v>4</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="8">
         <v>0.25</v>
       </c>
-      <c r="E52" s="14">
+      <c r="E52" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F52" t="s">
         <v>144</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2142,16 +2139,16 @@
       <c r="C53">
         <v>1</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="8" t="s">
         <v>149</v>
       </c>
       <c r="F53" t="s">
         <v>148</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2165,17 +2162,17 @@
       <c r="C54">
         <v>1</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="8">
         <v>0.18</v>
       </c>
-      <c r="E54" s="14">
+      <c r="E54" s="8">
         <f>D54*C54</f>
         <v>0.18</v>
       </c>
       <c r="F54" t="s">
         <v>156</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2189,18 +2186,18 @@
       <c r="C55">
         <v>1</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="8">
         <f>0.08</f>
         <v>0.08</v>
       </c>
-      <c r="E55" s="14">
+      <c r="E55" s="8">
         <f>C55*D55</f>
         <v>0.08</v>
       </c>
       <c r="F55" t="s">
         <v>145</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G55" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2223,28 +2220,29 @@
       <c r="F56" t="s">
         <v>46</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="6" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="C3:C15"/>
-    <mergeCell ref="D3:D15"/>
-    <mergeCell ref="E3:E15"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="F3:F15"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="C3:C15"/>
+    <mergeCell ref="D3:D15"/>
+    <mergeCell ref="E3:E15"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F36" r:id="rId1" xr:uid="{FB074A23-A170-4AA1-BEF8-B664F65AFCC8}"/>
+    <hyperlink ref="F41" r:id="rId2" xr:uid="{861F2286-11CA-4AC5-AE87-612BD01BD190}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
